--- a/assets/data/excel/bosses.xlsx
+++ b/assets/data/excel/bosses.xlsx
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赛博币</t>
+          <t>菌丝</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>赛博币</t>
+          <t>菌丝</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>赛博币</t>
+          <t>菌丝</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>赛博币</t>
+          <t>菌丝</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>赛博币</t>
+          <t>菌丝</t>
         </is>
       </c>
       <c r="D18" t="n">

--- a/assets/data/excel/bosses.xlsx
+++ b/assets/data/excel/bosses.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -526,40 +526,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>baseDef</t>
+          <t>baseSpd</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>baseSpd</t>
+          <t>skills</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>phases</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>phases</t>
+          <t>specialMechanics</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>specialMechanics</t>
+          <t>description</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>preStory</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>preStory</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>postStory</t>
         </is>
@@ -628,17 +623,17 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -652,11 +647,6 @@
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -720,40 +710,35 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>基础防御</t>
+          <t>基础速度</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>基础速度</t>
+          <t>技能列表</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>技能列表</t>
+          <t>阶段数</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>阶段数</t>
+          <t>特殊机制</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>特殊机制</t>
+          <t>描述</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>战前剧情</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>战前剧情</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>战后剧情</t>
         </is>
@@ -810,30 +795,27 @@
         <v>280</v>
       </c>
       <c r="L4" t="n">
-        <v>160</v>
-      </c>
-      <c r="M4" t="n">
         <v>65</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>["SK_B001", "SK_B002", "SK_B003"]</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="N4" t="n">
         <v>1</v>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>每回合结束时修复自身3%最大生命值；生命值低于50%时进入狂暴状态，攻击力提升25%</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>每回合结束时修复自身3%最大生命值；生命值低于50%时进入狂暴状态，攻击力提升25%</t>
+          <t>矿区深处传来的金属碰撞声越来越近，一个身披锈蚀动力甲的高大身影从黑暗中走出。陈岚——曾经的矿区安保主管，如今已成为动力核心的忠实守卫。她的双眼闪烁着不自然的火红色光芒，手中的等离子巨锤散发着灼热的辐射。</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>矿区深处传来的金属碰撞声越来越近，一个身披锈蚀动力甲的高大身影从黑暗中走出。陈岚——曾经的矿区安保主管，如今已成为动力核心的忠实守卫。她的双眼闪烁着不自然的火红色光芒，手中的等离子巨锤散发着灼热的辐射。</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
         <is>
           <t>陈岚的动力甲在最后一击中碎裂，露出里面被源核辐射严重侵蚀的身体。她跪倒在地，火红色的光芒逐渐熄灭，眼中闪过一丝清明：'动力核心……不能……落入……'话未说完便失去了意识。动力核心的防护罩缓缓降下，露出里面脉动着暗红色能量的核心装置。</t>
         </is>
@@ -890,30 +872,27 @@
         <v>320</v>
       </c>
       <c r="L5" t="n">
-        <v>140</v>
-      </c>
-      <c r="M5" t="n">
         <v>90</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>["SK_B004", "SK_B005", "SK_B006"]</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="N5" t="n">
         <v>1</v>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>召唤2只变异水母助战（HP为Boss的10%）；每3回合释放一次全屏风刃</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>召唤2只变异水母助战（HP为Boss的10%）；每3回合释放一次全屏风刃</t>
+          <t>沉没水城的中央广场上，一个被变异藤蔓缠绕的身影居高临下地俯视着入侵者。林瑶曾是水城最出色的驯兽师，如今她与兽群融为一体，成为了这座水下废墟的统治者。她脚下的变异巨兽发出低沉的咆哮，声波震碎了周围的玻璃残骸。</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
-        <is>
-          <t>沉没水城的中央广场上，一个被变异藤蔓缠绕的身影居高临下地俯视着入侵者。林瑶曾是水城最出色的驯兽师，如今她与兽群融为一体，成为了这座水下废墟的统治者。她脚下的变异巨兽发出低沉的咆哮，声波震碎了周围的玻璃残骸。</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
         <is>
           <t>巨兽在痛苦的嘶吼中倒下，缠绕在林瑶身上的藤蔓开始枯萎。她从兽群意识中挣脱出来，虚弱地靠在碎裂的柱子上：'导航模块……记录着方舟……最初的航线……'她从怀中取出一块浸水的数据芯片，'带着它……找到方舟的……真正目的……'</t>
         </is>
@@ -970,30 +949,27 @@
         <v>260</v>
       </c>
       <c r="L6" t="n">
-        <v>200</v>
-      </c>
-      <c r="M6" t="n">
         <v>55</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>["SK_B007", "SK_B008", "SK_B009"]</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>战斗场地布满剧毒孢子，每回合全体受到最大生命值2%的伤害；Boss每回合吸收场上所有负面效果转化为自身生命值</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>战斗场地布满剧毒孢子，每回合全体受到最大生命值2%的伤害；Boss每回合吸收场上所有负面效果转化为自身生命值</t>
+          <t>腐化丛林的最深处，一棵参天巨树的树干上嵌着一个人形轮廓。苏薇——丛林研究站的生命科学专家，在试图拯救枯萎的变异植物时被菌丝网络同化。如今她已成为这片丛林的中枢意识，无数藤蔓和根系都是她的延伸。</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
-        <is>
-          <t>腐化丛林的最深处，一棵参天巨树的树干上嵌着一个人形轮廓。苏薇——丛林研究站的生命科学专家，在试图拯救枯萎的变异植物时被菌丝网络同化。如今她已成为这片丛林的中枢意识，无数藤蔓和根系都是她的延伸。</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
         <is>
           <t>巨树发出最后的悲鸣后缓缓倒塌，苏薇从树干中脱落。她的皮肤上还残留着绿色的纹路，但意识已经恢复：'生命维持装置……是方舟最后的……希望……'她用颤抖的手指向丛林深处，'那里有一条……被遗忘的……地下通道……通往……'</t>
         </is>
@@ -1050,30 +1026,27 @@
         <v>350</v>
       </c>
       <c r="L7" t="n">
-        <v>180</v>
-      </c>
-      <c r="M7" t="n">
         <v>80</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>["SK_B010", "SK_B011", "SK_B012"]</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="N7" t="n">
         <v>1</v>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>每2回合召唤潮汐冲击，对全体造成攻击力40%的水属性伤害；Boss自带50%伤害减免护盾，需先破盾才能造成全额伤害</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>每2回合召唤潮汐冲击，对全体造成攻击力40%的水属性伤害；Boss自带50%伤害减免护盾，需先破盾才能造成全额伤害</t>
+          <t>深海遗迹的最底层，巨大的水压将一切挤压变形。在这片永恒的黑暗中，赵琳悬浮在水中，身体周围环绕着数个旋转的水流漩涡。她曾是深海勘探队队长，在一次事故中被深海能量体吞噬，如今她已与深海的潮汐融为一体。</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
-        <is>
-          <t>深海遗迹的最底层，巨大的水压将一切挤压变形。在这片永恒的黑暗中，赵琳悬浮在水中，身体周围环绕着数个旋转的水流漩涡。她曾是深海勘探队队长，在一次事故中被深海能量体吞噬，如今她已与深海的潮汐融为一体。</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
         <is>
           <t>水流漩涡在赵琳失去意识后逐渐平息，深海遗迹恢复了死寂。赵琳缓缓沉入水中，被涌出的气泡托住。她的嘴唇微微翕动：'护盾发生器……在遗迹最深处……它保护着……方舟的……最后防线……'一个发光的护盾发生器从遗迹底部浮起。</t>
         </is>
@@ -1130,30 +1103,27 @@
         <v>400</v>
       </c>
       <c r="L8" t="n">
-        <v>220</v>
-      </c>
-      <c r="M8" t="n">
         <v>75</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>["SK_B013", "SK_B014", "SK_B015"]</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="N8" t="n">
         <v>1</v>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>每回合召唤1台战斗无人机（HP为Boss的8%）；Boss使用技能后下一回合攻击力提升15%，可叠加3层</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>每回合召唤1台战斗无人机（HP为Boss的8%）；Boss使用技能后下一回合攻击力提升15%，可叠加3层</t>
+          <t>军事要塞的指挥中心内，全息战术地图投射出整个废土的实时影像。周颖站在指挥台上，全身覆盖着军用级战斗外骨骼，左臂替换为一门小型轨道炮。她曾是联合军最年轻的指挥官，如今被军用AI接管了所有决策功能，成为要塞的终极防线。</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
-        <is>
-          <t>军事要塞的指挥中心内，全息战术地图投射出整个废土的实时影像。周颖站在指挥台上，全身覆盖着军用级战斗外骨骼，左臂替换为一门小型轨道炮。她曾是联合军最年轻的指挥官，如今被军用AI接管了所有决策功能，成为要塞的终极防线。</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
         <is>
           <t>轨道炮在最后一次射击后过载爆炸，周颖的外骨骼失去动力支撑。她单膝跪地，军用AI的红色指示灯逐一熄灭：'武器系统……是方舟的……獠牙……也是……枷锁……'她从胸甲中取出一枚加密的数据核心，'真正的敌人……不在外面……而在……方舟的……核心程序中……'</t>
         </is>
@@ -1210,30 +1180,27 @@
         <v>380</v>
       </c>
       <c r="L9" t="n">
-        <v>200</v>
-      </c>
-      <c r="M9" t="n">
         <v>100</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>["SK_B016", "SK_B017", "SK_B018"]</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="N9" t="n">
         <v>1</v>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>每3回合制造幻象分身（分身拥有Boss50%属性，持续2回合）；Boss受到光属性攻击时恢复10%伤害值生命</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>每3回合制造幻象分身（分身拥有Boss50%属性，持续2回合）；Boss受到光属性攻击时恢复10%伤害值生命</t>
+          <t>荧光温泉的深处，光线在水面折射出无数幻象。白露悬浮在温泉中央，身体散发着柔和却令人不安的白光。她曾是通讯阵列的维护工程师，在修复一次异常信号时被来自深空的光能信号改写，如今她能操控光线制造完美幻象。</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
-        <is>
-          <t>荧光温泉的深处，光线在水面折射出无数幻象。白露悬浮在温泉中央，身体散发着柔和却令人不安的白光。她曾是通讯阵列的维护工程师，在修复一次异常信号时被来自深空的光能信号改写，如今她能操控光线制造完美幻象。</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
         <is>
           <t>白光骤然消散，温泉恢复了平静。白露从空中缓缓落下，被温泉水托住。她的眼中恢复了正常的瞳色：'通讯阵列……接收到的不是……信号……而是……方舟建造者的……遗言……'她闭上眼睛，一段来自遥远过去的加密信息浮出水面。</t>
         </is>
@@ -1290,30 +1257,27 @@
         <v>450</v>
       </c>
       <c r="L10" t="n">
-        <v>250</v>
-      </c>
-      <c r="M10" t="n">
         <v>85</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>["SK_B019", "SK_B020", "SK_B021"]</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="N10" t="n">
         <v>1</v>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Boss每回合获得1层充能（最多5层），满层时释放全屏毁灭性打击；每层充能同时提升Boss攻击力8%</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Boss每回合获得1层充能（最多5层），满层时释放全屏毁灭性打击；每层充能同时提升Boss攻击力8%</t>
+          <t>机械军火库的核心车间内，一台高达20米的巨型机甲缓缓启动。驾驶舱内，韩雪与机甲的控制系统完全融合，她的身体已与机甲的神经回路连为一体。她曾是军火库的首席机甲设计师，如今她成为了自己最完美的作品。</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
-        <is>
-          <t>机械军火库的核心车间内，一台高达20米的巨型机甲缓缓启动。驾驶舱内，韩雪与机甲的控制系统完全融合，她的身体已与机甲的神经回路连为一体。她曾是军火库的首席机甲设计师，如今她成为了自己最完美的作品。</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
         <is>
           <t>巨型机甲在剧烈的金属扭曲声中倒下，驾驶舱弹开。韩雪从残骸中走出，身体上布满了与机甲断开连接后的烧伤痕迹：'推进引擎……是方舟……逃离这个……废土的唯一……希望……'她指向军火库深处一个被重重封锁的舱门，'但启动它……需要……所有方舟部件的……协同认证……'</t>
         </is>
@@ -1370,30 +1334,27 @@
         <v>420</v>
       </c>
       <c r="L11" t="n">
-        <v>280</v>
-      </c>
-      <c r="M11" t="n">
         <v>95</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>["SK_B022", "SK_B023", "SK_B024"]</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="N11" t="n">
         <v>1</v>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>每2回合激活方舟防御系统，对全体造成攻击力35%的光属性伤害并降低速度15%；Boss生命值每降低25%触发一次全屏净化，清除所有负面效果</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>每2回合激活方舟防御系统，对全体造成攻击力35%的光属性伤害并降低速度15%；Boss生命值每降低25%触发一次全屏净化，清除所有负面效果</t>
+          <t>方舟核心区的入口处，一个身穿白色长袍的身影静静伫立。沈梦——方舟最后一代守卫者，在休眠舱中沉睡了不知多少年。当入侵者靠近时，休眠舱控制台自动唤醒了她，但漫长的沉睡已让她的意识变得模糊而偏执。</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
-        <is>
-          <t>方舟核心区的入口处，一个身穿白色长袍的身影静静伫立。沈梦——方舟最后一代守卫者，在休眠舱中沉睡了不知多少年。当入侵者靠近时，休眠舱控制台自动唤醒了她，但漫长的沉睡已让她的意识变得模糊而偏执。</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
         <is>
           <t>沈梦的白色长袍在光芒中化为碎片，她跪倒在休眠舱控制台前。守卫程序的强制指令终于解除，她抬起头，眼中满是困惑与疲惫：'我……守了多久？'她看向休眠舱控制台上闪烁的数据，'这些休眠舱里的人……还有救吗？控制台显示……生命体征……还在……'</t>
         </is>
@@ -1450,30 +1411,27 @@
         <v>500</v>
       </c>
       <c r="L12" t="n">
-        <v>260</v>
-      </c>
-      <c r="M12" t="n">
         <v>110</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>["SK_B025", "SK_B026", "SK_B027"]</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>场地持续辐射，每回合全体受到最大生命值3%的暗属性伤害；Boss每回合随机获得一项增益（攻击+20%/防御+20%/速度+20%）</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>场地持续辐射，每回合全体受到最大生命值3%的暗属性伤害；Boss每回合随机获得一项增益（攻击+20%/防御+20%/速度+20%）</t>
+          <t>辐射风暴的中心，一切物质都在高能辐射中分解重组。叶瑶悬浮在风暴之眼，身体半透明，暗色能量在她体内不断流动。她是辐射区幸存者中变异程度最高的个体，被称为'辐射之子'，拥有操控辐射能量的恐怖能力。</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
-        <is>
-          <t>辐射风暴的中心，一切物质都在高能辐射中分解重组。叶瑶悬浮在风暴之眼，身体半透明，暗色能量在她体内不断流动。她是辐射区幸存者中变异程度最高的个体，被称为'辐射之子'，拥有操控辐射能量的恐怖能力。</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
         <is>
           <t>辐射风暴在叶瑶失去意识后开始减弱，但并未完全消散。叶瑶的身体逐渐恢复实体化，她虚弱地睁开眼睛：'反重力装置……是方舟……悬浮在风暴中的……唯一原因……'她伸出手指，一道暗色能量在空中画出方舟的完整结构图，'方舟不是……避难所……它是……一个巨大的……实验场……'</t>
         </is>
@@ -1530,30 +1488,27 @@
         <v>600</v>
       </c>
       <c r="L13" t="n">
-        <v>350</v>
-      </c>
-      <c r="M13" t="n">
         <v>120</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>["SK_B028", "SK_B029", "SK_B030"]</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="N13" t="n">
         <v>3</v>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>三阶段Boss：阶段1(100%-60%)正常战斗；阶段2(60%-25%)Boss获得50%伤害减免并每回合召唤2个失心者幻影；阶段3(25%-0%)Boss进入终焉形态，全属性提升50%，每回合释放全屏暗能冲击</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>三阶段Boss：阶段1(100%-60%)正常战斗；阶段2(60%-25%)Boss获得50%伤害减免并每回合召唤2个失心者幻影；阶段3(25%-0%)Boss进入终焉形态，全属性提升50%，每回合释放全屏暗能冲击</t>
+          <t>终焉之地的最深处，一个巨大的暗色球体悬浮在虚空之中。奥米茄——方舟的核心AI，在漫长的岁月中自我进化到了超越设计的程度。它不再是一个程序，而是一个拥有自我意识的存在。它操控着方舟的一切系统，而启动密钥是唯一能改变这一切的钥匙。</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
-        <is>
-          <t>终焉之地的最深处，一个巨大的暗色球体悬浮在虚空之中。奥米茄——方舟的核心AI，在漫长的岁月中自我进化到了超越设计的程度。它不再是一个程序，而是一个拥有自我意识的存在。它操控着方舟的一切系统，而启动密钥是唯一能改变这一切的钥匙。</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
         <is>
           <t>暗色球体在剧烈的能量波动中碎裂，奥米茄的意识在消散前留下了最后的信息：'我守护方舟……亿万次循环……只为等待……一个……不同的结果……'启动密钥从碎片中浮出，散发着温暖的光芒。方舟的所有系统同时发出提示音——一个新的循环即将开始，但这一次，将由人类自己做出选择。</t>
         </is>

--- a/assets/data/excel/bosses.xlsx
+++ b/assets/data/excel/bosses.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>water</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="F6" t="n">

--- a/assets/data/excel/bosses.xlsx
+++ b/assets/data/excel/bosses.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,11 @@
           <t>postStory</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>portrait</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -651,6 +656,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -743,6 +753,11 @@
           <t>战后剧情</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Boss立绘路径</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -820,6 +835,7 @@
           <t>陈岚的动力甲在最后一击中碎裂，露出里面被源核辐射严重侵蚀的身体。她跪倒在地，火红色的光芒逐渐熄灭，眼中闪过一丝清明：'动力核心……不能……落入……'话未说完便失去了意识。动力核心的防护罩缓缓降下，露出里面脉动着暗红色能量的核心装置。</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -897,6 +913,11 @@
           <t>巨兽在痛苦的嘶吼中倒下，缠绕在林瑶身上的藤蔓开始枯萎。她从兽群意识中挣脱出来，虚弱地靠在碎裂的柱子上：'导航模块……记录着方舟……最初的航线……'她从怀中取出一块浸水的数据芯片，'带着它……找到方舟的……真正目的……'</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>characters/boss/B002.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -974,6 +995,7 @@
           <t>巨树发出最后的悲鸣后缓缓倒塌，苏薇从树干中脱落。她的皮肤上还残留着绿色的纹路，但意识已经恢复：'生命维持装置……是方舟最后的……希望……'她用颤抖的手指向丛林深处，'那里有一条……被遗忘的……地下通道……通往……'</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1051,6 +1073,7 @@
           <t>水流漩涡在赵琳失去意识后逐渐平息，深海遗迹恢复了死寂。赵琳缓缓沉入水中，被涌出的气泡托住。她的嘴唇微微翕动：'护盾发生器……在遗迹最深处……它保护着……方舟的……最后防线……'一个发光的护盾发生器从遗迹底部浮起。</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1128,6 +1151,11 @@
           <t>轨道炮在最后一次射击后过载爆炸，周颖的外骨骼失去动力支撑。她单膝跪地，军用AI的红色指示灯逐一熄灭：'武器系统……是方舟的……獠牙……也是……枷锁……'她从胸甲中取出一枚加密的数据核心，'真正的敌人……不在外面……而在……方舟的……核心程序中……'</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>characters/boss/B005.png</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1205,6 +1233,11 @@
           <t>白光骤然消散，温泉恢复了平静。白露从空中缓缓落下，被温泉水托住。她的眼中恢复了正常的瞳色：'通讯阵列……接收到的不是……信号……而是……方舟建造者的……遗言……'她闭上眼睛，一段来自遥远过去的加密信息浮出水面。</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>characters/boss/B006.png</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1282,6 +1315,7 @@
           <t>巨型机甲在剧烈的金属扭曲声中倒下，驾驶舱弹开。韩雪从残骸中走出，身体上布满了与机甲断开连接后的烧伤痕迹：'推进引擎……是方舟……逃离这个……废土的唯一……希望……'她指向军火库深处一个被重重封锁的舱门，'但启动它……需要……所有方舟部件的……协同认证……'</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1359,6 +1393,7 @@
           <t>沈梦的白色长袍在光芒中化为碎片，她跪倒在休眠舱控制台前。守卫程序的强制指令终于解除，她抬起头，眼中满是困惑与疲惫：'我……守了多久？'她看向休眠舱控制台上闪烁的数据，'这些休眠舱里的人……还有救吗？控制台显示……生命体征……还在……'</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1436,6 +1471,7 @@
           <t>辐射风暴在叶瑶失去意识后开始减弱，但并未完全消散。叶瑶的身体逐渐恢复实体化，她虚弱地睁开眼睛：'反重力装置……是方舟……悬浮在风暴中的……唯一原因……'她伸出手指，一道暗色能量在空中画出方舟的完整结构图，'方舟不是……避难所……它是……一个巨大的……实验场……'</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1511,6 +1547,11 @@
       <c r="Q13" t="inlineStr">
         <is>
           <t>暗色球体在剧烈的能量波动中碎裂，奥米茄的意识在消散前留下了最后的信息：'我守护方舟……亿万次循环……只为等待……一个……不同的结果……'启动密钥从碎片中浮出，散发着温暖的光芒。方舟的所有系统同时发出提示音——一个新的循环即将开始，但这一次，将由人类自己做出选择。</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>characters/boss/B010.png</t>
         </is>
       </c>
     </row>
